--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2017/NORTH_DAKOTA_2017.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2017/NORTH_DAKOTA_2017.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -470,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -501,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Ignacio Zaragoza</t>
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -558,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -573,7 +613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -589,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -602,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Total</t>
@@ -633,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -646,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -659,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Total</t>
@@ -674,7 +739,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -690,9 +755,14 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C23">
@@ -703,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -716,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Total</t>
@@ -747,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>San José Iturbide</t>
@@ -760,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Total</t>
@@ -780,7 +870,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C29">
@@ -791,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C30">
@@ -804,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -817,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Total</t>
@@ -837,7 +942,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cuautepec de Hinojosa</t>
+          <t>Cuautepec De Hinojosa</t>
         </is>
       </c>
       <c r="C33">
@@ -848,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Total</t>
@@ -868,7 +978,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C35">
@@ -879,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Casimiro Castillo</t>
@@ -892,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -905,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -918,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -931,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -944,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>San Julián</t>
@@ -957,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -970,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -983,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C44">
@@ -996,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -1009,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zapotlán del Rey</t>
+          <t>Zapotlán Del Rey</t>
         </is>
       </c>
       <c r="C46">
@@ -1022,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1053,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -1066,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Los Reyes</t>
@@ -1079,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Maravatío</t>
@@ -1092,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Villamar</t>
@@ -1105,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1136,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -1149,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1180,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1211,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>General Terán</t>
@@ -1224,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -1237,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1268,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C64">
@@ -1281,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>San Lorenzo Texmelúcan</t>
@@ -1294,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Santa María Peñoles</t>
@@ -1307,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1338,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Nealtican</t>
@@ -1351,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Pantepec</t>
@@ -1364,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tetela de Ocampo</t>
+          <t>Tetela De Ocampo</t>
         </is>
       </c>
       <c r="C71">
@@ -1377,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1408,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -1421,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1452,9 +1727,14 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Santa María del Río</t>
+          <t>Santa María Del Río</t>
         </is>
       </c>
       <c r="C77">
@@ -1465,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1496,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Mocorito</t>
@@ -1509,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1540,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1571,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1602,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1633,9 +1943,14 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nochistlán de Mejía</t>
+          <t>Nochistlán De Mejía</t>
         </is>
       </c>
       <c r="C89">
@@ -1646,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -1659,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1682,76 +2007,6 @@
       </c>
       <c r="D92">
         <v>1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 826,856</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Junio de 2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
